--- a/TC/아이템버닝PLUS_TC.xlsx
+++ b/TC/아이템버닝PLUS_TC.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\leegm0430\01_포토폴리오\TC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\leegm0430\01_포토폴리오\TC\TC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130A42E8-6142-4F3C-B9AC-BE8B884435EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09436D5F-C843-4573-B833-C4DAC4EDC125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="필수항목TC" sheetId="1" r:id="rId1"/>
@@ -2000,9 +2000,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2016,6 +2013,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2354,21 +2354,28 @@
   <dimension ref="A1:N41"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="9" style="22" customWidth="1"/>
-    <col min="2" max="2" width="9.3984375" style="22" customWidth="1"/>
-    <col min="3" max="3" width="12.8984375" style="22" customWidth="1"/>
-    <col min="4" max="4" width="11.19921875" style="22" customWidth="1"/>
-    <col min="5" max="5" width="15.09765625" style="22" customWidth="1"/>
-    <col min="6" max="7" width="21.09765625" style="22" customWidth="1"/>
-    <col min="8" max="8" width="44" style="22" customWidth="1"/>
-    <col min="9" max="9" width="33.5" style="22" customWidth="1"/>
-    <col min="10" max="10" width="23.69921875" style="22" customWidth="1"/>
-    <col min="13" max="13" width="26.3984375" style="22" customWidth="1"/>
-    <col min="14" max="14" width="26.8984375" style="22" customWidth="1"/>
+    <col min="1" max="1" width="9" style="21" customWidth="1"/>
+    <col min="2" max="2" width="9.3984375" style="21" customWidth="1"/>
+    <col min="3" max="3" width="12.8984375" style="21" customWidth="1"/>
+    <col min="4" max="4" width="11.19921875" style="21" customWidth="1"/>
+    <col min="5" max="5" width="15.09765625" style="21" customWidth="1"/>
+    <col min="6" max="7" width="21.09765625" style="21" customWidth="1"/>
+    <col min="8" max="8" width="44" style="21" customWidth="1"/>
+    <col min="9" max="9" width="33.5" style="21" customWidth="1"/>
+    <col min="10" max="10" width="23.69921875" style="21" customWidth="1"/>
+    <col min="13" max="13" width="26.3984375" style="21" customWidth="1"/>
+    <col min="14" max="14" width="26.8984375" style="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:10" ht="15" customHeight="1" thickBot="1">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="I2" s="4" t="s">
         <v>0</v>
       </c>
@@ -2377,6 +2384,13 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="15" customHeight="1" thickBot="1">
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
       <c r="I3" s="4" t="s">
         <v>2</v>
       </c>
@@ -2385,6 +2399,13 @@
       </c>
     </row>
     <row r="4" spans="2:10" ht="18" customHeight="1" thickBot="1">
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
       <c r="I4" s="4" t="s">
         <v>3</v>
       </c>
@@ -2428,10 +2449,10 @@
       <c r="C6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="7" t="s">
         <v>438</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -2455,10 +2476,10 @@
       <c r="C7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="7" t="s">
         <v>234</v>
       </c>
       <c r="F7" s="6" t="s">
@@ -2482,10 +2503,10 @@
       <c r="C8" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="7" t="s">
         <v>447</v>
       </c>
       <c r="F8" s="7" t="s">
@@ -2509,10 +2530,10 @@
       <c r="C9" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="7" t="s">
         <v>452</v>
       </c>
       <c r="F9" s="7" t="s">
@@ -2536,10 +2557,10 @@
       <c r="C10" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="7" t="s">
         <v>268</v>
       </c>
       <c r="F10" s="7" t="s">
@@ -2563,10 +2584,10 @@
       <c r="C11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="7" t="s">
         <v>273</v>
       </c>
       <c r="F11" s="13" t="s">
@@ -2590,10 +2611,10 @@
       <c r="C12" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="7" t="s">
         <v>255</v>
       </c>
       <c r="F12" s="13" t="s">
@@ -2617,10 +2638,10 @@
       <c r="C13" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="7" t="s">
         <v>292</v>
       </c>
       <c r="F13" s="13" t="s">
@@ -2644,10 +2665,10 @@
       <c r="C14" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="7" t="s">
         <v>473</v>
       </c>
       <c r="F14" s="7" t="s">
@@ -2671,10 +2692,10 @@
       <c r="C15" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="7" t="s">
         <v>311</v>
       </c>
       <c r="F15" s="7" t="s">
@@ -2698,10 +2719,10 @@
       <c r="C16" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="17" t="s">
+      <c r="D16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>482</v>
       </c>
       <c r="F16" s="7" t="s">
@@ -2725,10 +2746,10 @@
       <c r="C17" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="17" t="s">
+      <c r="D17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>487</v>
       </c>
       <c r="F17" s="7" t="s">
@@ -2752,10 +2773,10 @@
       <c r="C18" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="17" t="s">
+      <c r="D18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>492</v>
       </c>
       <c r="F18" s="7" t="s">
@@ -2779,10 +2800,10 @@
       <c r="C19" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="7" t="s">
         <v>497</v>
       </c>
       <c r="F19" s="14" t="s">
@@ -2806,10 +2827,10 @@
       <c r="C20" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="7" t="s">
         <v>502</v>
       </c>
       <c r="F20" s="15" t="s">
@@ -2833,10 +2854,10 @@
       <c r="C21" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="7" t="s">
         <v>507</v>
       </c>
       <c r="F21" s="15" t="s">
@@ -2860,10 +2881,10 @@
       <c r="C22" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="7" t="s">
         <v>512</v>
       </c>
       <c r="F22" s="7" t="s">
@@ -2887,10 +2908,10 @@
       <c r="C23" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="7" t="s">
         <v>331</v>
       </c>
       <c r="F23" s="7" t="s">
@@ -2914,10 +2935,10 @@
       <c r="C24" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="7" t="s">
         <v>520</v>
       </c>
       <c r="F24" s="7" t="s">
@@ -2941,10 +2962,10 @@
       <c r="C25" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="7" t="s">
         <v>525</v>
       </c>
       <c r="F25" s="13" t="s">
@@ -2968,10 +2989,10 @@
       <c r="C26" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="7" t="s">
         <v>530</v>
       </c>
       <c r="F26" s="7" t="s">
@@ -2995,10 +3016,10 @@
       <c r="C27" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="7" t="s">
         <v>535</v>
       </c>
       <c r="F27" s="7" t="s">
@@ -3022,10 +3043,10 @@
       <c r="C28" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="7" t="s">
         <v>325</v>
       </c>
       <c r="F28" s="7" t="s">
@@ -3049,10 +3070,10 @@
       <c r="C29" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="7" t="s">
         <v>400</v>
       </c>
       <c r="F29" s="7" t="s">
@@ -3076,10 +3097,10 @@
       <c r="C30" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="7" t="s">
         <v>422</v>
       </c>
       <c r="F30" s="7" t="s">
@@ -3103,10 +3124,10 @@
       <c r="C31" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="7" t="s">
         <v>364</v>
       </c>
       <c r="F31" s="7" t="s">
@@ -3130,10 +3151,10 @@
       <c r="C32" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="7" t="s">
         <v>273</v>
       </c>
       <c r="F32" s="10" t="s">
@@ -3266,21 +3287,29 @@
   <dimension ref="A1:N130"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="9" style="22" customWidth="1"/>
-    <col min="2" max="2" width="9.3984375" style="22" customWidth="1"/>
-    <col min="3" max="3" width="12.8984375" style="22" customWidth="1"/>
-    <col min="4" max="4" width="11.19921875" style="22" customWidth="1"/>
-    <col min="5" max="5" width="15.09765625" style="22" customWidth="1"/>
-    <col min="6" max="7" width="21.09765625" style="22" customWidth="1"/>
-    <col min="8" max="8" width="44" style="22" customWidth="1"/>
-    <col min="9" max="9" width="35.8984375" style="22" customWidth="1"/>
-    <col min="10" max="10" width="29.3984375" style="22" customWidth="1"/>
-    <col min="13" max="13" width="26.3984375" style="22" customWidth="1"/>
-    <col min="14" max="14" width="26.8984375" style="22" customWidth="1"/>
+    <col min="1" max="1" width="9" style="21" customWidth="1"/>
+    <col min="2" max="2" width="9.3984375" style="21" customWidth="1"/>
+    <col min="3" max="3" width="12.8984375" style="21" customWidth="1"/>
+    <col min="4" max="4" width="11.19921875" style="21" customWidth="1"/>
+    <col min="5" max="5" width="15.09765625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="21.09765625" style="21" customWidth="1"/>
+    <col min="7" max="7" width="51.19921875" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="44" style="21" customWidth="1"/>
+    <col min="9" max="9" width="47.3984375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="29.3984375" style="21" customWidth="1"/>
+    <col min="13" max="13" width="26.3984375" style="21" customWidth="1"/>
+    <col min="14" max="14" width="26.8984375" style="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:10" ht="15" customHeight="1" thickBot="1">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="I2" s="4" t="s">
         <v>0</v>
       </c>
@@ -3289,6 +3318,13 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="15" customHeight="1" thickBot="1">
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
       <c r="I3" s="4" t="s">
         <v>2</v>
       </c>
@@ -3297,10 +3333,17 @@
       </c>
     </row>
     <row r="4" spans="2:10">
-      <c r="I4" s="20" t="s">
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="20" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3340,13 +3383,13 @@
       <c r="C6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="7" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="7" t="s">
@@ -3358,7 +3401,7 @@
       <c r="I6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="18"/>
+      <c r="J6" s="17"/>
     </row>
     <row r="7" spans="2:10" ht="43.2">
       <c r="B7" s="6">
@@ -3367,25 +3410,25 @@
       <c r="C7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="D7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="17" t="s">
         <v>25</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="18"/>
+      <c r="J7" s="17"/>
     </row>
     <row r="8" spans="2:10" ht="57.6">
       <c r="B8" s="6">
@@ -3394,10 +3437,10 @@
       <c r="C8" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="17" t="s">
+      <c r="D8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>22</v>
       </c>
       <c r="F8" s="7" t="s">
@@ -3421,13 +3464,13 @@
       <c r="C9" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="17" t="s">
+      <c r="D9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G9" s="7" t="s">
@@ -3448,13 +3491,13 @@
       <c r="C10" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="17" t="s">
+      <c r="D10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="7" t="s">
         <v>36</v>
       </c>
       <c r="G10" s="7" t="s">
@@ -3475,13 +3518,13 @@
       <c r="C11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="17" t="s">
+      <c r="D11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G11" s="7" t="s">
@@ -3502,13 +3545,13 @@
       <c r="C12" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="17" t="s">
+      <c r="D12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="7" t="s">
         <v>27</v>
       </c>
       <c r="G12" s="7" t="s">
@@ -3529,13 +3572,13 @@
       <c r="C13" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="17" t="s">
+      <c r="D13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G13" s="7" t="s">
@@ -3556,13 +3599,13 @@
       <c r="C14" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="17" t="s">
+      <c r="D14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="7" t="s">
         <v>36</v>
       </c>
       <c r="G14" s="7" t="s">
@@ -3583,13 +3626,13 @@
       <c r="C15" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="17" t="s">
+      <c r="D15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G15" s="10" t="s">
@@ -3610,16 +3653,16 @@
       <c r="C16" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="17" t="s">
+      <c r="D16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="7" t="s">
         <v>53</v>
       </c>
       <c r="H16" s="10" t="s">
@@ -3637,16 +3680,16 @@
       <c r="C17" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="17" t="s">
+      <c r="D17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="17" t="s">
+      <c r="G17" s="7" t="s">
         <v>56</v>
       </c>
       <c r="H17" s="7" t="s">
@@ -3664,16 +3707,16 @@
       <c r="C18" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="17" t="s">
+      <c r="D18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G18" s="17" t="s">
+      <c r="G18" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H18" s="10" t="s">
@@ -3691,16 +3734,16 @@
       <c r="C19" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="17" t="s">
+      <c r="D19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="17" t="s">
+      <c r="G19" s="7" t="s">
         <v>64</v>
       </c>
       <c r="H19" s="13" t="s">
@@ -3718,16 +3761,16 @@
       <c r="C20" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="17" t="s">
+      <c r="D20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G20" s="17" t="s">
+      <c r="G20" s="7" t="s">
         <v>67</v>
       </c>
       <c r="H20" s="15" t="s">
@@ -3745,16 +3788,16 @@
       <c r="C21" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="17" t="s">
+      <c r="D21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="17" t="s">
+      <c r="G21" s="7" t="s">
         <v>70</v>
       </c>
       <c r="H21" s="7" t="s">
@@ -3772,16 +3815,16 @@
       <c r="C22" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="17" t="s">
+      <c r="D22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G22" s="17" t="s">
+      <c r="G22" s="7" t="s">
         <v>72</v>
       </c>
       <c r="H22" s="7" t="s">
@@ -3799,16 +3842,16 @@
       <c r="C23" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="17" t="s">
+      <c r="D23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G23" s="17" t="s">
+      <c r="G23" s="7" t="s">
         <v>74</v>
       </c>
       <c r="H23" s="7" t="s">
@@ -3826,16 +3869,16 @@
       <c r="C24" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="D24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G24" s="17" t="s">
+      <c r="G24" s="7" t="s">
         <v>76</v>
       </c>
       <c r="H24" s="7" t="s">
@@ -3853,16 +3896,16 @@
       <c r="C25" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="17" t="s">
+      <c r="D25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="F25" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G25" s="17" t="s">
+      <c r="G25" s="7" t="s">
         <v>78</v>
       </c>
       <c r="H25" s="7" t="s">
@@ -3880,16 +3923,16 @@
       <c r="C26" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="17" t="s">
+      <c r="D26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="F26" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G26" s="17" t="s">
+      <c r="G26" s="7" t="s">
         <v>81</v>
       </c>
       <c r="H26" s="7" t="s">
@@ -3907,16 +3950,16 @@
       <c r="C27" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="17" t="s">
+      <c r="D27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="F27" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G27" s="17" t="s">
+      <c r="G27" s="7" t="s">
         <v>84</v>
       </c>
       <c r="H27" s="7" t="s">
@@ -3934,16 +3977,16 @@
       <c r="C28" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="17" t="s">
+      <c r="D28" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G28" s="17" t="s">
+      <c r="G28" s="7" t="s">
         <v>86</v>
       </c>
       <c r="H28" s="7" t="s">
@@ -3961,16 +4004,16 @@
       <c r="C29" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="17" t="s">
+      <c r="D29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="F29" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G29" s="17" t="s">
+      <c r="G29" s="7" t="s">
         <v>88</v>
       </c>
       <c r="H29" s="7" t="s">
@@ -3988,16 +4031,16 @@
       <c r="C30" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="17" t="s">
+      <c r="D30" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F30" s="17" t="s">
+      <c r="F30" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G30" s="17" t="s">
+      <c r="G30" s="7" t="s">
         <v>90</v>
       </c>
       <c r="H30" s="7" t="s">
@@ -4006,7 +4049,7 @@
       <c r="I30" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J30" s="19"/>
+      <c r="J30" s="18"/>
     </row>
     <row r="31" spans="2:10" ht="57.6">
       <c r="B31" s="6">
@@ -4015,16 +4058,16 @@
       <c r="C31" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="17" t="s">
+      <c r="D31" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F31" s="17" t="s">
+      <c r="F31" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G31" s="17" t="s">
+      <c r="G31" s="7" t="s">
         <v>92</v>
       </c>
       <c r="H31" s="7" t="s">
@@ -4042,16 +4085,16 @@
       <c r="C32" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="17" t="s">
+      <c r="D32" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G32" s="17" t="s">
+      <c r="G32" s="7" t="s">
         <v>95</v>
       </c>
       <c r="H32" s="7" t="s">
@@ -4069,16 +4112,16 @@
       <c r="C33" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="17" t="s">
+      <c r="D33" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="F33" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G33" s="17" t="s">
+      <c r="G33" s="7" t="s">
         <v>98</v>
       </c>
       <c r="H33" s="7" t="s">
@@ -4096,16 +4139,16 @@
       <c r="C34" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D34" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="17" t="s">
+      <c r="D34" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="F34" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G34" s="17" t="s">
+      <c r="G34" s="7" t="s">
         <v>99</v>
       </c>
       <c r="H34" s="7" t="s">
@@ -4123,16 +4166,16 @@
       <c r="C35" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D35" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="17" t="s">
+      <c r="D35" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G35" s="17" t="s">
+      <c r="G35" s="7" t="s">
         <v>101</v>
       </c>
       <c r="H35" s="7" t="s">
@@ -4150,16 +4193,16 @@
       <c r="C36" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D36" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="17" t="s">
+      <c r="D36" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F36" s="17" t="s">
+      <c r="F36" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G36" s="17" t="s">
+      <c r="G36" s="7" t="s">
         <v>103</v>
       </c>
       <c r="H36" s="7" t="s">
@@ -4177,16 +4220,16 @@
       <c r="C37" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="17" t="s">
+      <c r="D37" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G37" s="17" t="s">
+      <c r="G37" s="7" t="s">
         <v>105</v>
       </c>
       <c r="H37" s="7" t="s">
@@ -4204,16 +4247,16 @@
       <c r="C38" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D38" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="17" t="s">
+      <c r="D38" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="F38" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G38" s="17" t="s">
+      <c r="G38" s="7" t="s">
         <v>108</v>
       </c>
       <c r="H38" s="7" t="s">
@@ -4231,16 +4274,16 @@
       <c r="C39" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="17" t="s">
+      <c r="D39" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F39" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G39" s="7" t="s">
         <v>111</v>
       </c>
       <c r="H39" s="7" t="s">
@@ -4258,16 +4301,16 @@
       <c r="C40" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D40" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="17" t="s">
+      <c r="D40" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="17" t="s">
+      <c r="F40" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G40" s="17" t="s">
+      <c r="G40" s="7" t="s">
         <v>113</v>
       </c>
       <c r="H40" s="7" t="s">
@@ -4285,16 +4328,16 @@
       <c r="C41" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D41" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="17" t="s">
+      <c r="D41" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F41" s="17" t="s">
+      <c r="F41" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G41" s="17" t="s">
+      <c r="G41" s="7" t="s">
         <v>115</v>
       </c>
       <c r="H41" s="7" t="s">
@@ -4312,16 +4355,16 @@
       <c r="C42" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" s="17" t="s">
+      <c r="D42" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="F42" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G42" s="17" t="s">
+      <c r="G42" s="7" t="s">
         <v>117</v>
       </c>
       <c r="H42" s="13" t="s">
@@ -4339,16 +4382,16 @@
       <c r="C43" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D43" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" s="17" t="s">
+      <c r="D43" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F43" s="17" t="s">
+      <c r="F43" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G43" s="17" t="s">
+      <c r="G43" s="7" t="s">
         <v>119</v>
       </c>
       <c r="H43" s="7" t="s">
@@ -4366,16 +4409,16 @@
       <c r="C44" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D44" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44" s="17" t="s">
+      <c r="D44" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F44" s="17" t="s">
+      <c r="F44" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G44" s="17" t="s">
+      <c r="G44" s="7" t="s">
         <v>122</v>
       </c>
       <c r="H44" s="6" t="s">
@@ -4393,16 +4436,16 @@
       <c r="C45" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D45" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E45" s="17" t="s">
+      <c r="D45" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="F45" s="17" t="s">
+      <c r="F45" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G45" s="17" t="s">
+      <c r="G45" s="7" t="s">
         <v>125</v>
       </c>
       <c r="H45" s="6" t="s">
@@ -4420,16 +4463,16 @@
       <c r="C46" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D46" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46" s="17" t="s">
+      <c r="D46" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="F46" s="17" t="s">
+      <c r="F46" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G46" s="17" t="s">
+      <c r="G46" s="7" t="s">
         <v>126</v>
       </c>
       <c r="H46" s="7" t="s">
@@ -4447,16 +4490,16 @@
       <c r="C47" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D47" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47" s="17" t="s">
+      <c r="D47" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="F47" s="17" t="s">
+      <c r="F47" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G47" s="17" t="s">
+      <c r="G47" s="7" t="s">
         <v>128</v>
       </c>
       <c r="H47" s="7" t="s">
@@ -4474,16 +4517,16 @@
       <c r="C48" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D48" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="17" t="s">
+      <c r="D48" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="F48" s="17" t="s">
+      <c r="F48" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G48" s="17" t="s">
+      <c r="G48" s="7" t="s">
         <v>130</v>
       </c>
       <c r="H48" s="10" t="s">
@@ -4501,16 +4544,16 @@
       <c r="C49" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D49" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E49" s="17" t="s">
+      <c r="D49" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="F49" s="17" t="s">
+      <c r="F49" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G49" s="17" t="s">
+      <c r="G49" s="7" t="s">
         <v>132</v>
       </c>
       <c r="H49" s="6" t="s">
@@ -4528,16 +4571,16 @@
       <c r="C50" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D50" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E50" s="17" t="s">
+      <c r="D50" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="F50" s="17" t="s">
+      <c r="F50" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G50" s="17" t="s">
+      <c r="G50" s="7" t="s">
         <v>135</v>
       </c>
       <c r="H50" s="10" t="s">
@@ -4555,16 +4598,16 @@
       <c r="C51" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D51" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E51" s="17" t="s">
+      <c r="D51" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F51" s="17" t="s">
+      <c r="F51" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="17" t="s">
+      <c r="G51" s="7" t="s">
         <v>138</v>
       </c>
       <c r="H51" s="10" t="s">
@@ -4582,16 +4625,16 @@
       <c r="C52" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D52" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E52" s="17" t="s">
+      <c r="D52" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F52" s="17" t="s">
+      <c r="F52" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G52" s="17" t="s">
+      <c r="G52" s="7" t="s">
         <v>140</v>
       </c>
       <c r="H52" s="7" t="s">
@@ -4609,16 +4652,16 @@
       <c r="C53" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D53" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E53" s="17" t="s">
+      <c r="D53" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F53" s="17" t="s">
+      <c r="F53" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G53" s="17" t="s">
+      <c r="G53" s="7" t="s">
         <v>142</v>
       </c>
       <c r="H53" s="7" t="s">
@@ -4636,16 +4679,16 @@
       <c r="C54" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D54" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E54" s="17" t="s">
+      <c r="D54" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E54" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F54" s="17" t="s">
+      <c r="F54" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G54" s="17" t="s">
+      <c r="G54" s="7" t="s">
         <v>144</v>
       </c>
       <c r="H54" s="10" t="s">
@@ -4663,16 +4706,16 @@
       <c r="C55" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D55" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E55" s="17" t="s">
+      <c r="D55" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E55" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F55" s="17" t="s">
+      <c r="F55" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G55" s="17" t="s">
+      <c r="G55" s="7" t="s">
         <v>146</v>
       </c>
       <c r="H55" s="10" t="s">
@@ -4690,16 +4733,16 @@
       <c r="C56" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D56" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E56" s="17" t="s">
+      <c r="D56" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F56" s="17" t="s">
+      <c r="F56" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G56" s="17" t="s">
+      <c r="G56" s="7" t="s">
         <v>149</v>
       </c>
       <c r="H56" s="10" t="s">
@@ -4717,16 +4760,16 @@
       <c r="C57" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D57" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E57" s="17" t="s">
+      <c r="D57" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F57" s="17" t="s">
+      <c r="F57" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G57" s="17" t="s">
+      <c r="G57" s="7" t="s">
         <v>152</v>
       </c>
       <c r="H57" s="10" t="s">
@@ -4744,16 +4787,16 @@
       <c r="C58" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D58" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E58" s="17" t="s">
+      <c r="D58" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E58" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F58" s="17" t="s">
+      <c r="F58" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G58" s="17" t="s">
+      <c r="G58" s="7" t="s">
         <v>153</v>
       </c>
       <c r="H58" s="7" t="s">
@@ -4771,16 +4814,16 @@
       <c r="C59" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D59" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E59" s="17" t="s">
+      <c r="D59" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E59" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F59" s="17" t="s">
+      <c r="F59" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G59" s="17" t="s">
+      <c r="G59" s="7" t="s">
         <v>155</v>
       </c>
       <c r="H59" s="10" t="s">
@@ -4798,16 +4841,16 @@
       <c r="C60" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D60" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E60" s="17" t="s">
+      <c r="D60" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E60" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F60" s="17" t="s">
+      <c r="F60" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G60" s="17" t="s">
+      <c r="G60" s="7" t="s">
         <v>157</v>
       </c>
       <c r="H60" s="7" t="s">
@@ -4825,16 +4868,16 @@
       <c r="C61" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D61" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E61" s="17" t="s">
+      <c r="D61" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F61" s="17" t="s">
+      <c r="F61" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G61" s="17" t="s">
+      <c r="G61" s="7" t="s">
         <v>159</v>
       </c>
       <c r="H61" s="10" t="s">
@@ -4852,16 +4895,16 @@
       <c r="C62" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D62" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E62" s="17" t="s">
+      <c r="D62" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E62" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F62" s="17" t="s">
+      <c r="F62" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G62" s="17" t="s">
+      <c r="G62" s="7" t="s">
         <v>162</v>
       </c>
       <c r="H62" s="7" t="s">
@@ -4879,16 +4922,16 @@
       <c r="C63" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D63" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E63" s="17" t="s">
+      <c r="D63" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F63" s="17" t="s">
+      <c r="F63" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G63" s="17" t="s">
+      <c r="G63" s="7" t="s">
         <v>165</v>
       </c>
       <c r="H63" s="7" t="s">
@@ -4906,16 +4949,16 @@
       <c r="C64" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D64" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E64" s="17" t="s">
+      <c r="D64" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F64" s="17" t="s">
+      <c r="F64" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G64" s="17" t="s">
+      <c r="G64" s="7" t="s">
         <v>167</v>
       </c>
       <c r="H64" s="7" t="s">
@@ -4933,16 +4976,16 @@
       <c r="C65" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E65" s="17" t="s">
+      <c r="D65" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F65" s="17" t="s">
+      <c r="F65" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G65" s="17" t="s">
+      <c r="G65" s="7" t="s">
         <v>169</v>
       </c>
       <c r="H65" s="7" t="s">
@@ -4960,16 +5003,16 @@
       <c r="C66" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D66" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E66" s="17" t="s">
+      <c r="D66" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E66" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F66" s="17" t="s">
+      <c r="F66" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G66" s="17" t="s">
+      <c r="G66" s="7" t="s">
         <v>171</v>
       </c>
       <c r="H66" s="7" t="s">
@@ -4987,16 +5030,16 @@
       <c r="C67" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D67" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E67" s="17" t="s">
+      <c r="D67" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E67" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F67" s="17" t="s">
+      <c r="F67" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G67" s="17" t="s">
+      <c r="G67" s="7" t="s">
         <v>173</v>
       </c>
       <c r="H67" s="7" t="s">
@@ -5014,16 +5057,16 @@
       <c r="C68" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D68" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E68" s="17" t="s">
+      <c r="D68" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F68" s="17" t="s">
+      <c r="F68" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G68" s="17" t="s">
+      <c r="G68" s="7" t="s">
         <v>176</v>
       </c>
       <c r="H68" s="7" t="s">
@@ -5041,16 +5084,16 @@
       <c r="C69" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D69" s="17" t="s">
+      <c r="D69" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E69" s="17" t="s">
+      <c r="E69" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="F69" s="17" t="s">
+      <c r="F69" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="G69" s="17" t="s">
+      <c r="G69" s="7" t="s">
         <v>181</v>
       </c>
       <c r="H69" s="7" t="s">
@@ -5068,16 +5111,16 @@
       <c r="C70" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D70" s="17" t="s">
+      <c r="D70" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E70" s="17" t="s">
+      <c r="E70" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="F70" s="17" t="s">
+      <c r="F70" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="G70" s="17" t="s">
+      <c r="G70" s="7" t="s">
         <v>185</v>
       </c>
       <c r="H70" s="10" t="s">
@@ -5095,16 +5138,16 @@
       <c r="C71" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D71" s="17" t="s">
+      <c r="D71" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E71" s="17" t="s">
+      <c r="E71" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="F71" s="17" t="s">
+      <c r="F71" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="G71" s="17" t="s">
+      <c r="G71" s="7" t="s">
         <v>189</v>
       </c>
       <c r="H71" s="10" t="s">
@@ -5122,19 +5165,19 @@
       <c r="C72" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E72" s="17" t="s">
+      <c r="E72" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="F72" s="17" t="s">
+      <c r="F72" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="G72" s="17" t="s">
+      <c r="G72" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="H72" s="18" t="s">
+      <c r="H72" s="17" t="s">
         <v>194</v>
       </c>
       <c r="I72" s="10" t="s">
@@ -5149,16 +5192,16 @@
       <c r="C73" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D73" s="17" t="s">
+      <c r="D73" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E73" s="17" t="s">
+      <c r="E73" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="F73" s="17" t="s">
+      <c r="F73" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="G73" s="17" t="s">
+      <c r="G73" s="7" t="s">
         <v>198</v>
       </c>
       <c r="H73" s="10" t="s">
@@ -5176,16 +5219,16 @@
       <c r="C74" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D74" s="17" t="s">
+      <c r="D74" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E74" s="17" t="s">
+      <c r="E74" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="F74" s="17" t="s">
+      <c r="F74" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="G74" s="17" t="s">
+      <c r="G74" s="7" t="s">
         <v>202</v>
       </c>
       <c r="H74" s="10" t="s">
@@ -5203,13 +5246,13 @@
       <c r="C75" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D75" s="17" t="s">
+      <c r="D75" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E75" s="17" t="s">
+      <c r="E75" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="F75" s="17" t="s">
+      <c r="F75" s="7" t="s">
         <v>206</v>
       </c>
       <c r="G75" s="7" t="s">
@@ -5230,13 +5273,13 @@
       <c r="C76" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D76" s="17" t="s">
+      <c r="D76" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E76" s="17" t="s">
+      <c r="E76" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="F76" s="17" t="s">
+      <c r="F76" s="7" t="s">
         <v>211</v>
       </c>
       <c r="G76" s="7" t="s">
@@ -5257,13 +5300,13 @@
       <c r="C77" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D77" s="17" t="s">
+      <c r="D77" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E77" s="17" t="s">
+      <c r="E77" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="F77" s="17" t="s">
+      <c r="F77" s="7" t="s">
         <v>215</v>
       </c>
       <c r="G77" s="7" t="s">
@@ -5284,13 +5327,13 @@
       <c r="C78" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D78" s="17" t="s">
+      <c r="D78" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E78" s="17" t="s">
+      <c r="E78" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="F78" s="17" t="s">
+      <c r="F78" s="7" t="s">
         <v>221</v>
       </c>
       <c r="G78" s="7" t="s">
@@ -5311,13 +5354,13 @@
       <c r="C79" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D79" s="17" t="s">
+      <c r="D79" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E79" s="17" t="s">
+      <c r="E79" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="F79" s="17" t="s">
+      <c r="F79" s="7" t="s">
         <v>225</v>
       </c>
       <c r="G79" s="7" t="s">
@@ -5338,13 +5381,13 @@
       <c r="C80" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D80" s="17" t="s">
+      <c r="D80" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E80" s="17" t="s">
+      <c r="E80" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="F80" s="17" t="s">
+      <c r="F80" s="7" t="s">
         <v>230</v>
       </c>
       <c r="G80" s="7" t="s">
@@ -5365,13 +5408,13 @@
       <c r="C81" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D81" s="17" t="s">
+      <c r="D81" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E81" s="17" t="s">
+      <c r="E81" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="F81" s="17" t="s">
+      <c r="F81" s="7" t="s">
         <v>235</v>
       </c>
       <c r="G81" s="7" t="s">
@@ -5392,13 +5435,13 @@
       <c r="C82" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D82" s="17" t="s">
+      <c r="D82" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E82" s="17" t="s">
+      <c r="E82" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="F82" s="17" t="s">
+      <c r="F82" s="7" t="s">
         <v>240</v>
       </c>
       <c r="G82" s="7" t="s">
@@ -5419,13 +5462,13 @@
       <c r="C83" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D83" s="17" t="s">
+      <c r="D83" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E83" s="17" t="s">
+      <c r="E83" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="F83" s="17" t="s">
+      <c r="F83" s="7" t="s">
         <v>245</v>
       </c>
       <c r="G83" s="7" t="s">
@@ -5446,13 +5489,13 @@
       <c r="C84" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D84" s="17" t="s">
+      <c r="D84" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E84" s="17" t="s">
+      <c r="E84" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="F84" s="17" t="s">
+      <c r="F84" s="7" t="s">
         <v>251</v>
       </c>
       <c r="G84" s="7" t="s">
@@ -5473,13 +5516,13 @@
       <c r="C85" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D85" s="17" t="s">
+      <c r="D85" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E85" s="17" t="s">
+      <c r="E85" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="F85" s="17" t="s">
+      <c r="F85" s="7" t="s">
         <v>256</v>
       </c>
       <c r="G85" s="7" t="s">
@@ -5500,13 +5543,13 @@
       <c r="C86" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D86" s="17" t="s">
+      <c r="D86" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E86" s="17" t="s">
+      <c r="E86" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="F86" s="17" t="s">
+      <c r="F86" s="7" t="s">
         <v>260</v>
       </c>
       <c r="G86" s="7" t="s">
@@ -5527,13 +5570,13 @@
       <c r="C87" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D87" s="17" t="s">
+      <c r="D87" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E87" s="17" t="s">
+      <c r="E87" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="F87" s="17" t="s">
+      <c r="F87" s="7" t="s">
         <v>264</v>
       </c>
       <c r="G87" s="7" t="s">
@@ -5554,13 +5597,13 @@
       <c r="C88" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D88" s="17" t="s">
+      <c r="D88" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E88" s="17" t="s">
+      <c r="E88" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="F88" s="17" t="s">
+      <c r="F88" s="7" t="s">
         <v>269</v>
       </c>
       <c r="G88" s="7" t="s">
@@ -5581,13 +5624,13 @@
       <c r="C89" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D89" s="17" t="s">
+      <c r="D89" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E89" s="17" t="s">
+      <c r="E89" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="F89" s="17" t="s">
+      <c r="F89" s="7" t="s">
         <v>274</v>
       </c>
       <c r="G89" s="7" t="s">
@@ -5608,13 +5651,13 @@
       <c r="C90" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D90" s="17" t="s">
+      <c r="D90" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E90" s="17" t="s">
+      <c r="E90" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="F90" s="17" t="s">
+      <c r="F90" s="7" t="s">
         <v>278</v>
       </c>
       <c r="G90" s="7" t="s">
@@ -5635,13 +5678,13 @@
       <c r="C91" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D91" s="17" t="s">
+      <c r="D91" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E91" s="17" t="s">
+      <c r="E91" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="F91" s="17" t="s">
+      <c r="F91" s="7" t="s">
         <v>282</v>
       </c>
       <c r="G91" s="7" t="s">
@@ -5662,13 +5705,13 @@
       <c r="C92" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D92" s="17" t="s">
+      <c r="D92" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E92" s="17" t="s">
+      <c r="E92" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="F92" s="17" t="s">
+      <c r="F92" s="7" t="s">
         <v>288</v>
       </c>
       <c r="G92" s="7" t="s">
@@ -5689,13 +5732,13 @@
       <c r="C93" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D93" s="17" t="s">
+      <c r="D93" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E93" s="17" t="s">
+      <c r="E93" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="F93" s="17" t="s">
+      <c r="F93" s="7" t="s">
         <v>293</v>
       </c>
       <c r="G93" s="7" t="s">
@@ -5716,13 +5759,13 @@
       <c r="C94" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D94" s="17" t="s">
+      <c r="D94" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E94" s="17" t="s">
+      <c r="E94" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="F94" s="17" t="s">
+      <c r="F94" s="7" t="s">
         <v>298</v>
       </c>
       <c r="G94" s="7" t="s">
@@ -5743,13 +5786,13 @@
       <c r="C95" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D95" s="17" t="s">
+      <c r="D95" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E95" s="17" t="s">
+      <c r="E95" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="F95" s="17" t="s">
+      <c r="F95" s="7" t="s">
         <v>303</v>
       </c>
       <c r="G95" s="7" t="s">
@@ -5770,13 +5813,13 @@
       <c r="C96" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D96" s="17" t="s">
+      <c r="D96" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E96" s="17" t="s">
+      <c r="E96" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="F96" s="17" t="s">
+      <c r="F96" s="7" t="s">
         <v>307</v>
       </c>
       <c r="G96" s="7" t="s">
@@ -5797,13 +5840,13 @@
       <c r="C97" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D97" s="17" t="s">
+      <c r="D97" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E97" s="17" t="s">
+      <c r="E97" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="F97" s="17" t="s">
+      <c r="F97" s="7" t="s">
         <v>312</v>
       </c>
       <c r="G97" s="7" t="s">
@@ -5824,13 +5867,13 @@
       <c r="C98" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D98" s="17" t="s">
+      <c r="D98" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E98" s="17" t="s">
+      <c r="E98" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="F98" s="17" t="s">
+      <c r="F98" s="7" t="s">
         <v>316</v>
       </c>
       <c r="G98" s="7" t="s">
@@ -5851,13 +5894,13 @@
       <c r="C99" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D99" s="17" t="s">
+      <c r="D99" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E99" s="17" t="s">
+      <c r="E99" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="F99" s="17" t="s">
+      <c r="F99" s="7" t="s">
         <v>320</v>
       </c>
       <c r="G99" s="7" t="s">
@@ -5878,13 +5921,13 @@
       <c r="C100" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="D100" s="17" t="s">
+      <c r="D100" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E100" s="17" t="s">
+      <c r="E100" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="F100" s="17" t="s">
+      <c r="F100" s="7" t="s">
         <v>326</v>
       </c>
       <c r="G100" s="7" t="s">
@@ -5905,13 +5948,13 @@
       <c r="C101" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D101" s="17" t="s">
+      <c r="D101" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="E101" s="17" t="s">
+      <c r="E101" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="F101" s="17" t="s">
+      <c r="F101" s="7" t="s">
         <v>332</v>
       </c>
       <c r="G101" s="7" t="s">
@@ -5932,13 +5975,13 @@
       <c r="C102" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D102" s="17" t="s">
+      <c r="D102" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="E102" s="17" t="s">
+      <c r="E102" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="F102" s="17" t="s">
+      <c r="F102" s="7" t="s">
         <v>337</v>
       </c>
       <c r="G102" s="7" t="s">
@@ -5959,13 +6002,13 @@
       <c r="C103" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D103" s="17" t="s">
+      <c r="D103" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="E103" s="17" t="s">
+      <c r="E103" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="F103" s="17" t="s">
+      <c r="F103" s="7" t="s">
         <v>341</v>
       </c>
       <c r="G103" s="7" t="s">
@@ -5986,13 +6029,13 @@
       <c r="C104" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D104" s="17" t="s">
+      <c r="D104" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="E104" s="17" t="s">
+      <c r="E104" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="F104" s="17" t="s">
+      <c r="F104" s="7" t="s">
         <v>346</v>
       </c>
       <c r="G104" s="7" t="s">
@@ -6013,13 +6056,13 @@
       <c r="C105" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D105" s="17" t="s">
+      <c r="D105" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="E105" s="17" t="s">
+      <c r="E105" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="F105" s="17" t="s">
+      <c r="F105" s="7" t="s">
         <v>350</v>
       </c>
       <c r="G105" s="7" t="s">
@@ -6040,13 +6083,13 @@
       <c r="C106" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D106" s="17" t="s">
+      <c r="D106" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="E106" s="17" t="s">
+      <c r="E106" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="F106" s="17" t="s">
+      <c r="F106" s="7" t="s">
         <v>355</v>
       </c>
       <c r="G106" s="7" t="s">
@@ -6067,16 +6110,16 @@
       <c r="C107" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D107" s="17" t="s">
+      <c r="D107" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="E107" s="17" t="s">
+      <c r="E107" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="F107" s="17" t="s">
+      <c r="F107" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="G107" s="17" t="s">
+      <c r="G107" s="7" t="s">
         <v>361</v>
       </c>
       <c r="H107" s="6" t="s">
@@ -6094,16 +6137,16 @@
       <c r="C108" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D108" s="17" t="s">
+      <c r="D108" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="E108" s="17" t="s">
+      <c r="E108" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="F108" s="17" t="s">
+      <c r="F108" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="G108" s="17" t="s">
+      <c r="G108" s="7" t="s">
         <v>366</v>
       </c>
       <c r="H108" s="6" t="s">
@@ -6121,16 +6164,16 @@
       <c r="C109" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="D109" s="17" t="s">
+      <c r="D109" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="E109" s="17" t="s">
+      <c r="E109" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="F109" s="17" t="s">
+      <c r="F109" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="G109" s="17" t="s">
+      <c r="G109" s="7" t="s">
         <v>370</v>
       </c>
       <c r="H109" s="6" t="s">
@@ -6148,13 +6191,13 @@
       <c r="C110" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="D110" s="17" t="s">
+      <c r="D110" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="E110" s="17" t="s">
+      <c r="E110" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="F110" s="17" t="s">
+      <c r="F110" s="7" t="s">
         <v>374</v>
       </c>
       <c r="G110" s="7" t="s">
@@ -6175,16 +6218,16 @@
       <c r="C111" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="D111" s="17" t="s">
+      <c r="D111" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="E111" s="17" t="s">
+      <c r="E111" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="F111" s="17" t="s">
+      <c r="F111" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="G111" s="17" t="s">
+      <c r="G111" s="7" t="s">
         <v>380</v>
       </c>
       <c r="H111" s="6" t="s">
@@ -6202,16 +6245,16 @@
       <c r="C112" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D112" s="17" t="s">
+      <c r="D112" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="E112" s="17" t="s">
+      <c r="E112" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="F112" s="17" t="s">
+      <c r="F112" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="G112" s="17" t="s">
+      <c r="G112" s="7" t="s">
         <v>386</v>
       </c>
       <c r="H112" s="6" t="s">
@@ -6229,16 +6272,16 @@
       <c r="C113" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D113" s="17" t="s">
+      <c r="D113" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="E113" s="17" t="s">
+      <c r="E113" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="F113" s="17" t="s">
+      <c r="F113" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="G113" s="17" t="s">
+      <c r="G113" s="7" t="s">
         <v>392</v>
       </c>
       <c r="H113" s="6" t="s">
@@ -6256,13 +6299,13 @@
       <c r="C114" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D114" s="17" t="s">
+      <c r="D114" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="E114" s="17" t="s">
+      <c r="E114" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="F114" s="17" t="s">
+      <c r="F114" s="7" t="s">
         <v>396</v>
       </c>
       <c r="G114" s="7" t="s">
@@ -6283,16 +6326,16 @@
       <c r="C115" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D115" s="17" t="s">
+      <c r="D115" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="E115" s="17" t="s">
+      <c r="E115" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="F115" s="17" t="s">
+      <c r="F115" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="G115" s="17" t="s">
+      <c r="G115" s="7" t="s">
         <v>402</v>
       </c>
       <c r="H115" s="6" t="s">
@@ -6310,16 +6353,16 @@
       <c r="C116" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D116" s="17" t="s">
+      <c r="D116" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="E116" s="17" t="s">
+      <c r="E116" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="F116" s="17" t="s">
+      <c r="F116" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="G116" s="17" t="s">
+      <c r="G116" s="7" t="s">
         <v>406</v>
       </c>
       <c r="H116" s="6" t="s">
@@ -6337,16 +6380,16 @@
       <c r="C117" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D117" s="17" t="s">
+      <c r="D117" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="E117" s="17" t="s">
+      <c r="E117" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="F117" s="17" t="s">
+      <c r="F117" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="G117" s="17" t="s">
+      <c r="G117" s="7" t="s">
         <v>410</v>
       </c>
       <c r="H117" s="6" t="s">
@@ -6364,13 +6407,13 @@
       <c r="C118" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="D118" s="17" t="s">
+      <c r="D118" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="E118" s="17" t="s">
+      <c r="E118" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="F118" s="17" t="s">
+      <c r="F118" s="7" t="s">
         <v>413</v>
       </c>
       <c r="G118" s="7" t="s">
@@ -6391,13 +6434,13 @@
       <c r="C119" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="D119" s="17" t="s">
+      <c r="D119" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="E119" s="17" t="s">
+      <c r="E119" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="F119" s="17" t="s">
+      <c r="F119" s="7" t="s">
         <v>417</v>
       </c>
       <c r="G119" s="7" t="s">
@@ -6418,13 +6461,13 @@
       <c r="C120" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D120" s="17" t="s">
+      <c r="D120" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="E120" s="17" t="s">
+      <c r="E120" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="F120" s="17" t="s">
+      <c r="F120" s="7" t="s">
         <v>423</v>
       </c>
       <c r="G120" s="7" t="s">
@@ -6445,13 +6488,13 @@
       <c r="C121" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="D121" s="17" t="s">
+      <c r="D121" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="E121" s="17" t="s">
+      <c r="E121" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="F121" s="17" t="s">
+      <c r="F121" s="7" t="s">
         <v>428</v>
       </c>
       <c r="G121" s="7" t="s">
@@ -6472,13 +6515,13 @@
       <c r="C122" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="D122" s="17" t="s">
+      <c r="D122" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="E122" s="17" t="s">
+      <c r="E122" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="F122" s="17" t="s">
+      <c r="F122" s="7" t="s">
         <v>433</v>
       </c>
       <c r="G122" s="7" t="s">
